--- a/versions/v1.xlsx
+++ b/versions/v1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NUIG\prj\v\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NUIG\prj\capstone prj\versions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E31ECDEE-64F9-455D-9281-5FC3C05BD419}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEB7BC49-3DA6-47D6-A0AF-69EEA57D632C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="10" windowWidth="19420" windowHeight="12220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1520" yWindow="1520" windowWidth="14280" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Seed_Formatted" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="115">
   <si>
     <t>ID</t>
   </si>
@@ -707,7 +707,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:E51"/>
   <sheetFormatPr defaultColWidth="41.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -732,7 +731,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -749,7 +748,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -766,7 +765,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -783,7 +782,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -800,7 +799,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -834,7 +833,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -851,7 +850,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -868,7 +867,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -885,7 +884,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -902,7 +901,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -919,7 +918,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -936,7 +935,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -953,7 +952,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -970,7 +969,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -987,7 +986,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1004,7 +1003,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1021,7 +1020,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1038,7 +1037,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1055,7 +1054,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1072,7 +1071,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1089,7 +1088,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1106,7 +1105,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1140,7 +1139,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1157,7 +1156,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1174,7 +1173,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1191,7 +1190,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1208,7 +1207,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1225,7 +1224,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1242,7 +1241,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1259,7 +1258,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1276,7 +1275,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1293,7 +1292,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1310,7 +1309,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1327,7 +1326,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1344,7 +1343,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1378,7 +1377,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1395,7 +1394,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1412,7 +1411,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>41</v>
       </c>
@@ -1429,7 +1428,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>42</v>
       </c>
@@ -1446,7 +1445,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>43</v>
       </c>
@@ -1463,7 +1462,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>44</v>
       </c>
@@ -1487,9 +1486,6 @@
       <c r="B46" t="s">
         <v>102</v>
       </c>
-      <c r="C46" t="s">
-        <v>20</v>
-      </c>
       <c r="D46" t="s">
         <v>103</v>
       </c>
@@ -1497,7 +1493,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>46</v>
       </c>
@@ -1514,7 +1510,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>47</v>
       </c>
@@ -1531,7 +1527,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>48</v>
       </c>
@@ -1548,7 +1544,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>49</v>
       </c>
@@ -1565,7 +1561,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>50</v>
       </c>
@@ -1583,13 +1579,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E51" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="Non-Homophobic"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:E51" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>